--- a/Sensors data.xlsx
+++ b/Sensors data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="16" documentId="8_{BF5B5FC1-64AA-4606-A780-2BA5CC58300E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{466086F6-596F-41F4-958E-1B5D71ADB341}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CBAF2CAF-A10F-4227-9339-64D5C6E0372A}"/>
+    <workbookView xWindow="2330" yWindow="1130" windowWidth="14400" windowHeight="8170" xr2:uid="{CBAF2CAF-A10F-4227-9339-64D5C6E0372A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
